--- a/doctool/test/auto/scenario21/システム機能設計書_サンプル_S21_レビュー記録票_expected.xlsx
+++ b/doctool/test/auto/scenario21/システム機能設計書_サンプル_S21_レビュー記録票_expected.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044E39EA-E2EF-452F-8E78-BDB0231FC11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F279FC89-4336-451C-8826-3538D9897411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1381,7 +1381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="206">
   <si>
     <t>レビュー対象物</t>
     <rPh sb="4" eb="7">
@@ -2643,9 +2643,6 @@
   </si>
   <si>
     <t>08/02山田</t>
-  </si>
-  <si>
-    <t>詳細設計</t>
   </si>
   <si>
     <t>取得できませんでした</t>
@@ -5177,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
